--- a/downloads/editable-xlsx/LS-TMP-017_Test_Data_Table.xlsx
+++ b/downloads/editable-xlsx/LS-TMP-017_Test_Data_Table.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="1" r:id="R3e8b271a1c544061"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="2" r:id="R5d3b5b5e1f0f488b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="1" r:id="Recbb5b9f46c948cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="2" r:id="Rbd5e297f84524de6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -43,8 +43,25 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF102033"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF102033"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -61,6 +78,21 @@
         <x:fgColor rgb="FFD6A23A"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0B1F3A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6D39A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -69,7 +101,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="25">
+  <x:cellXfs count="52">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -113,6 +145,75 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -271,93 +372,147 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="30" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="78.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="19.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="8.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="7" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12.25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="11.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="5" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="5.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="48" t="str">
         <x:v>LS-TMP-017 Test Data Table Template</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="10" t="str">
-        <x:v>LockwoodSTEM generic template for collecting repeatable engineering test data and calculating summary statistics.</x:v>
-      </x:c>
+      <x:c r="B1" s="48"/>
+      <x:c r="C1" s="48"/>
+      <x:c r="D1" s="48"/>
+      <x:c r="E1" s="48"/>
+      <x:c r="F1" s="48"/>
+      <x:c r="G1" s="48"/>
+      <x:c r="H1" s="48"/>
+      <x:c r="I1" s="48"/>
+      <x:c r="J1" s="48"/>
+      <x:c r="K1" s="48"/>
+    </x:row>
+    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A2" s="39" t="str">
+        <x:v>LockwoodSTEM template for collecting repeatable engineering test data and calculating summary statistics.</x:v>
+      </x:c>
+      <x:c r="B2" s="40"/>
+      <x:c r="C2" s="40"/>
+      <x:c r="D2" s="40"/>
+      <x:c r="E2" s="40"/>
+      <x:c r="F2" s="40"/>
+      <x:c r="G2" s="40"/>
+      <x:c r="H2" s="40"/>
+      <x:c r="I2" s="40"/>
+      <x:c r="J2" s="40"/>
+      <x:c r="K2" s="40"/>
+    </x:row>
+    <x:row r="3" ht="8" customHeight="1">
+      <x:c r="A3" s="49"/>
+      <x:c r="B3" s="49"/>
+      <x:c r="C3" s="49"/>
+      <x:c r="D3" s="49"/>
+      <x:c r="E3" s="49"/>
+      <x:c r="F3" s="49"/>
+      <x:c r="G3" s="49"/>
+      <x:c r="H3" s="49"/>
+      <x:c r="I3" s="49"/>
+      <x:c r="J3" s="49"/>
+      <x:c r="K3" s="49"/>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="16" t="str">
+      <x:c r="A4" s="47" t="str">
         <x:v>Project</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="str">
+      <x:c r="B4" s="47" t="str">
         <x:v>Test Name</x:v>
       </x:c>
-      <x:c r="C4" s="16" t="str">
+      <x:c r="C4" s="47" t="str">
         <x:v>Team / Student</x:v>
       </x:c>
-      <x:c r="D4" s="16" t="str">
+      <x:c r="D4" s="47" t="str">
         <x:v>Date</x:v>
       </x:c>
-      <x:c r="E4" s="16" t="str">
+      <x:c r="E4" s="47" t="str">
         <x:v>Indep. Var</x:v>
       </x:c>
-      <x:c r="F4" s="16" t="str">
+      <x:c r="F4" s="47" t="str">
         <x:v>Dep. Var</x:v>
       </x:c>
-      <x:c r="G4" s="16" t="str">
+      <x:c r="G4" s="47" t="str">
         <x:v>Controlled Vars</x:v>
       </x:c>
+      <x:c r="H4" s="47"/>
+      <x:c r="I4" s="47"/>
+      <x:c r="J4" s="47"/>
+      <x:c r="K4" s="47"/>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="22" t="str"/>
-      <x:c r="B5" s="22" t="str"/>
-      <x:c r="C5" s="22" t="str"/>
-      <x:c r="D5" s="22" t="str"/>
-      <x:c r="E5" s="22" t="str"/>
-      <x:c r="F5" s="22" t="str"/>
-      <x:c r="G5" s="22" t="str"/>
+      <x:c r="A5" s="23" t="str"/>
+      <x:c r="B5" s="23" t="str"/>
+      <x:c r="C5" s="23" t="str"/>
+      <x:c r="D5" s="23" t="str"/>
+      <x:c r="E5" s="23" t="str"/>
+      <x:c r="F5" s="23" t="str"/>
+      <x:c r="G5" s="23" t="str"/>
+      <x:c r="H5" s="23"/>
+      <x:c r="I5" s="23"/>
+      <x:c r="J5" s="23"/>
+      <x:c r="K5" s="23"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="23"/>
+      <x:c r="B6" s="23"/>
+      <x:c r="C6" s="23"/>
+      <x:c r="D6" s="23"/>
+      <x:c r="E6" s="23"/>
+      <x:c r="F6" s="23"/>
+      <x:c r="G6" s="23"/>
+      <x:c r="H6" s="23"/>
+      <x:c r="I6" s="23"/>
+      <x:c r="J6" s="23"/>
+      <x:c r="K6" s="23"/>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
-      <x:c r="A7" s="20" t="str">
+      <x:c r="A7" s="47" t="str">
         <x:v>Trial</x:v>
       </x:c>
-      <x:c r="B7" s="20" t="str">
+      <x:c r="B7" s="47" t="str">
         <x:v>Configuration / Condition</x:v>
       </x:c>
-      <x:c r="C7" s="20" t="str">
+      <x:c r="C7" s="47" t="str">
         <x:v>Independent Value</x:v>
       </x:c>
-      <x:c r="D7" s="20" t="str">
+      <x:c r="D7" s="47" t="str">
         <x:v>Measured Output</x:v>
       </x:c>
-      <x:c r="E7" s="20" t="str">
+      <x:c r="E7" s="47" t="str">
         <x:v>Units</x:v>
       </x:c>
-      <x:c r="F7" s="20" t="str">
+      <x:c r="F7" s="47" t="str">
         <x:v>Time (s)</x:v>
       </x:c>
-      <x:c r="G7" s="20" t="str">
+      <x:c r="G7" s="47" t="str">
         <x:v>Distance (m)</x:v>
       </x:c>
-      <x:c r="H7" s="20" t="str">
+      <x:c r="H7" s="47" t="str">
         <x:v>Velocity (m/s)</x:v>
       </x:c>
-      <x:c r="I7" s="20" t="str">
+      <x:c r="I7" s="47" t="str">
         <x:v>Notes</x:v>
       </x:c>
-      <x:c r="J7" s="20" t="str">
+      <x:c r="J7" s="47" t="str">
         <x:v>Valid?</x:v>
       </x:c>
-      <x:c r="K7" s="20" t="str">
+      <x:c r="K7" s="47" t="str">
         <x:v>Photo / Evidence Link</x:v>
       </x:c>
     </x:row>
@@ -741,65 +896,336 @@
       </x:c>
       <x:c r="K27" s="23" t="str"/>
     </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="23"/>
+      <x:c r="B28" s="23"/>
+      <x:c r="C28" s="23"/>
+      <x:c r="D28" s="23"/>
+      <x:c r="E28" s="23"/>
+      <x:c r="F28" s="23"/>
+      <x:c r="G28" s="23"/>
+      <x:c r="H28" s="23"/>
+      <x:c r="I28" s="23"/>
+      <x:c r="J28" s="23"/>
+      <x:c r="K28" s="23"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="23"/>
+      <x:c r="B29" s="23"/>
+      <x:c r="C29" s="23"/>
+      <x:c r="D29" s="23"/>
+      <x:c r="E29" s="23"/>
+      <x:c r="F29" s="23"/>
+      <x:c r="G29" s="23"/>
+      <x:c r="H29" s="23"/>
+      <x:c r="I29" s="23"/>
+      <x:c r="J29" s="23"/>
+      <x:c r="K29" s="23"/>
+    </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="18" t="str">
+      <x:c r="A30" s="50" t="str">
         <x:v>Summary Metric</x:v>
       </x:c>
-      <x:c r="B30" s="18" t="str">
+      <x:c r="B30" s="50" t="str">
         <x:v>Value</x:v>
       </x:c>
+      <x:c r="C30" s="23"/>
+      <x:c r="D30" s="23"/>
+      <x:c r="E30" s="23"/>
+      <x:c r="F30" s="23"/>
+      <x:c r="G30" s="23"/>
+      <x:c r="H30" s="23"/>
+      <x:c r="I30" s="23"/>
+      <x:c r="J30" s="23"/>
+      <x:c r="K30" s="23"/>
     </x:row>
     <x:row r="31" ht="22" customHeight="1">
       <x:c r="A31" s="23" t="str">
         <x:v>Avg Output</x:v>
       </x:c>
-      <x:c r="B31" s="22" t="str">
+      <x:c r="B31" s="23" t="str">
         <x:f>IFERROR(AVERAGEIF(J8:J27,"Yes",D8:D27),"")</x:f>
       </x:c>
+      <x:c r="C31" s="23"/>
+      <x:c r="D31" s="23"/>
+      <x:c r="E31" s="23"/>
+      <x:c r="F31" s="23"/>
+      <x:c r="G31" s="23"/>
+      <x:c r="H31" s="23"/>
+      <x:c r="I31" s="23"/>
+      <x:c r="J31" s="23"/>
+      <x:c r="K31" s="23"/>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
       <x:c r="A32" s="23" t="str">
         <x:v>Avg Velocity</x:v>
       </x:c>
-      <x:c r="B32" s="22" t="str">
+      <x:c r="B32" s="23" t="str">
         <x:f>IFERROR(AVERAGEIF(J8:J27,"Yes",H8:H27),"")</x:f>
       </x:c>
+      <x:c r="C32" s="23"/>
+      <x:c r="D32" s="23"/>
+      <x:c r="E32" s="23"/>
+      <x:c r="F32" s="23"/>
+      <x:c r="G32" s="23"/>
+      <x:c r="H32" s="23"/>
+      <x:c r="I32" s="23"/>
+      <x:c r="J32" s="23"/>
+      <x:c r="K32" s="23"/>
     </x:row>
     <x:row r="33" ht="22" customHeight="1">
       <x:c r="A33" s="23" t="str">
         <x:v>Best Velocity</x:v>
       </x:c>
-      <x:c r="B33" s="22" t="n">
+      <x:c r="B33" s="23" t="n">
         <x:f>IFERROR(MAX(H8:H27),"")</x:f>
         <x:v>0</x:v>
       </x:c>
+      <x:c r="C33" s="23"/>
+      <x:c r="D33" s="23"/>
+      <x:c r="E33" s="23"/>
+      <x:c r="F33" s="23"/>
+      <x:c r="G33" s="23"/>
+      <x:c r="H33" s="23"/>
+      <x:c r="I33" s="23"/>
+      <x:c r="J33" s="23"/>
+      <x:c r="K33" s="23"/>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
       <x:c r="A34" s="23" t="str">
         <x:v>Output Range</x:v>
       </x:c>
-      <x:c r="B34" s="22" t="n">
+      <x:c r="B34" s="23" t="n">
         <x:f>IFERROR(MAX(D8:D27)-MIN(D8:D27),"")</x:f>
         <x:v>0</x:v>
       </x:c>
+      <x:c r="C34" s="23"/>
+      <x:c r="D34" s="23"/>
+      <x:c r="E34" s="23"/>
+      <x:c r="F34" s="23"/>
+      <x:c r="G34" s="23"/>
+      <x:c r="H34" s="23"/>
+      <x:c r="I34" s="23"/>
+      <x:c r="J34" s="23"/>
+      <x:c r="K34" s="23"/>
     </x:row>
     <x:row r="35" ht="22" customHeight="1">
       <x:c r="A35" s="23" t="str">
         <x:v>Output St. Dev.</x:v>
       </x:c>
-      <x:c r="B35" s="22" t="n">
+      <x:c r="B35" s="23" t="n">
         <x:f>IFERROR(STDEV.S(D8:D27),"")</x:f>
         <x:v>0</x:v>
       </x:c>
+      <x:c r="C35" s="23"/>
+      <x:c r="D35" s="23"/>
+      <x:c r="E35" s="23"/>
+      <x:c r="F35" s="23"/>
+      <x:c r="G35" s="23"/>
+      <x:c r="H35" s="23"/>
+      <x:c r="I35" s="23"/>
+      <x:c r="J35" s="23"/>
+      <x:c r="K35" s="23"/>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="23" t="str">
         <x:v>Valid Trials</x:v>
       </x:c>
-      <x:c r="B36" s="22" t="n">
+      <x:c r="B36" s="23" t="n">
         <x:f>COUNTIF(J8:J27,"Yes")</x:f>
         <x:v>20</x:v>
       </x:c>
+      <x:c r="C36" s="23"/>
+      <x:c r="D36" s="23"/>
+      <x:c r="E36" s="23"/>
+      <x:c r="F36" s="23"/>
+      <x:c r="G36" s="23"/>
+      <x:c r="H36" s="23"/>
+      <x:c r="I36" s="23"/>
+      <x:c r="J36" s="23"/>
+      <x:c r="K36" s="23"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="23"/>
+      <x:c r="B37" s="23"/>
+      <x:c r="C37" s="23"/>
+      <x:c r="D37" s="23"/>
+      <x:c r="E37" s="23"/>
+      <x:c r="F37" s="23"/>
+      <x:c r="G37" s="23"/>
+      <x:c r="H37" s="23"/>
+      <x:c r="I37" s="23"/>
+      <x:c r="J37" s="23"/>
+      <x:c r="K37" s="23"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="23"/>
+      <x:c r="B38" s="23"/>
+      <x:c r="C38" s="23"/>
+      <x:c r="D38" s="23"/>
+      <x:c r="E38" s="23"/>
+      <x:c r="F38" s="23"/>
+      <x:c r="G38" s="23"/>
+      <x:c r="H38" s="23"/>
+      <x:c r="I38" s="23"/>
+      <x:c r="J38" s="23"/>
+      <x:c r="K38" s="23"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="23"/>
+      <x:c r="B39" s="23"/>
+      <x:c r="C39" s="23"/>
+      <x:c r="D39" s="23"/>
+      <x:c r="E39" s="23"/>
+      <x:c r="F39" s="23"/>
+      <x:c r="G39" s="23"/>
+      <x:c r="H39" s="23"/>
+      <x:c r="I39" s="23"/>
+      <x:c r="J39" s="23"/>
+      <x:c r="K39" s="23"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="23"/>
+      <x:c r="B40" s="23"/>
+      <x:c r="C40" s="23"/>
+      <x:c r="D40" s="23"/>
+      <x:c r="E40" s="23"/>
+      <x:c r="F40" s="23"/>
+      <x:c r="G40" s="23"/>
+      <x:c r="H40" s="23"/>
+      <x:c r="I40" s="23"/>
+      <x:c r="J40" s="23"/>
+      <x:c r="K40" s="23"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="23"/>
+      <x:c r="B41" s="23"/>
+      <x:c r="C41" s="23"/>
+      <x:c r="D41" s="23"/>
+      <x:c r="E41" s="23"/>
+      <x:c r="F41" s="23"/>
+      <x:c r="G41" s="23"/>
+      <x:c r="H41" s="23"/>
+      <x:c r="I41" s="23"/>
+      <x:c r="J41" s="23"/>
+      <x:c r="K41" s="23"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="23"/>
+      <x:c r="B42" s="23"/>
+      <x:c r="C42" s="23"/>
+      <x:c r="D42" s="23"/>
+      <x:c r="E42" s="23"/>
+      <x:c r="F42" s="23"/>
+      <x:c r="G42" s="23"/>
+      <x:c r="H42" s="23"/>
+      <x:c r="I42" s="23"/>
+      <x:c r="J42" s="23"/>
+      <x:c r="K42" s="23"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="23"/>
+      <x:c r="B43" s="23"/>
+      <x:c r="C43" s="23"/>
+      <x:c r="D43" s="23"/>
+      <x:c r="E43" s="23"/>
+      <x:c r="F43" s="23"/>
+      <x:c r="G43" s="23"/>
+      <x:c r="H43" s="23"/>
+      <x:c r="I43" s="23"/>
+      <x:c r="J43" s="23"/>
+      <x:c r="K43" s="23"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="23"/>
+      <x:c r="B44" s="23"/>
+      <x:c r="C44" s="23"/>
+      <x:c r="D44" s="23"/>
+      <x:c r="E44" s="23"/>
+      <x:c r="F44" s="23"/>
+      <x:c r="G44" s="23"/>
+      <x:c r="H44" s="23"/>
+      <x:c r="I44" s="23"/>
+      <x:c r="J44" s="23"/>
+      <x:c r="K44" s="23"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="23"/>
+      <x:c r="B45" s="23"/>
+      <x:c r="C45" s="23"/>
+      <x:c r="D45" s="23"/>
+      <x:c r="E45" s="23"/>
+      <x:c r="F45" s="23"/>
+      <x:c r="G45" s="23"/>
+      <x:c r="H45" s="23"/>
+      <x:c r="I45" s="23"/>
+      <x:c r="J45" s="23"/>
+      <x:c r="K45" s="23"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="23"/>
+      <x:c r="B46" s="23"/>
+      <x:c r="C46" s="23"/>
+      <x:c r="D46" s="23"/>
+      <x:c r="E46" s="23"/>
+      <x:c r="F46" s="23"/>
+      <x:c r="G46" s="23"/>
+      <x:c r="H46" s="23"/>
+      <x:c r="I46" s="23"/>
+      <x:c r="J46" s="23"/>
+      <x:c r="K46" s="23"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="23"/>
+      <x:c r="B47" s="23"/>
+      <x:c r="C47" s="23"/>
+      <x:c r="D47" s="23"/>
+      <x:c r="E47" s="23"/>
+      <x:c r="F47" s="23"/>
+      <x:c r="G47" s="23"/>
+      <x:c r="H47" s="23"/>
+      <x:c r="I47" s="23"/>
+      <x:c r="J47" s="23"/>
+      <x:c r="K47" s="23"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="23"/>
+      <x:c r="B48" s="23"/>
+      <x:c r="C48" s="23"/>
+      <x:c r="D48" s="23"/>
+      <x:c r="E48" s="23"/>
+      <x:c r="F48" s="23"/>
+      <x:c r="G48" s="23"/>
+      <x:c r="H48" s="23"/>
+      <x:c r="I48" s="23"/>
+      <x:c r="J48" s="23"/>
+      <x:c r="K48" s="23"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="23"/>
+      <x:c r="B49" s="23"/>
+      <x:c r="C49" s="23"/>
+      <x:c r="D49" s="23"/>
+      <x:c r="E49" s="23"/>
+      <x:c r="F49" s="23"/>
+      <x:c r="G49" s="23"/>
+      <x:c r="H49" s="23"/>
+      <x:c r="I49" s="23"/>
+      <x:c r="J49" s="23"/>
+      <x:c r="K49" s="23"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="23"/>
+      <x:c r="B50" s="23"/>
+      <x:c r="C50" s="23"/>
+      <x:c r="D50" s="23"/>
+      <x:c r="E50" s="23"/>
+      <x:c r="F50" s="23"/>
+      <x:c r="G50" s="23"/>
+      <x:c r="H50" s="23"/>
+      <x:c r="I50" s="23"/>
+      <x:c r="J50" s="23"/>
+      <x:c r="K50" s="23"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -822,28 +1248,33 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="80" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="25.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="57.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="6" t="str">
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="48" t="str">
         <x:v>How to Use This Template</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="23" t="str">
+      <x:c r="B1" s="48"/>
+    </x:row>
+    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A2" s="40"/>
+      <x:c r="B2" s="40"/>
+    </x:row>
+    <x:row r="3" ht="8" customHeight="1">
+      <x:c r="A3" s="49" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B3" s="23" t="str">
+      <x:c r="B3" s="49" t="str">
         <x:v>Define one independent variable and one dependent variable before testing.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="23" t="str">
+      <x:c r="A4" s="47" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B4" s="23" t="str">
+      <x:c r="B4" s="47" t="str">
         <x:v>Run repeatable trials under the same controlled conditions.</x:v>
       </x:c>
     </x:row>
@@ -864,16 +1295,190 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="23" t="str">
+      <x:c r="A7" s="47" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B7" s="23" t="str">
+      <x:c r="B7" s="47" t="str">
         <x:v>Attach or link photos, videos, or screenshots when evidence is required.</x:v>
       </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="23"/>
+      <x:c r="B8" s="23"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="23"/>
+      <x:c r="B9" s="23"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="23"/>
+      <x:c r="B10" s="23"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="23"/>
+      <x:c r="B11" s="23"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="23"/>
+      <x:c r="B12" s="23"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="23"/>
+      <x:c r="B13" s="23"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="23"/>
+      <x:c r="B14" s="23"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="23"/>
+      <x:c r="B15" s="23"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="23"/>
+      <x:c r="B16" s="23"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="23"/>
+      <x:c r="B17" s="23"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="23"/>
+      <x:c r="B18" s="23"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="23"/>
+      <x:c r="B19" s="23"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="23"/>
+      <x:c r="B20" s="23"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="23"/>
+      <x:c r="B21" s="23"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="23"/>
+      <x:c r="B22" s="23"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="23"/>
+      <x:c r="B23" s="23"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="23"/>
+      <x:c r="B24" s="23"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="23"/>
+      <x:c r="B25" s="23"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="23"/>
+      <x:c r="B26" s="23"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="23"/>
+      <x:c r="B27" s="23"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="23"/>
+      <x:c r="B28" s="23"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="23"/>
+      <x:c r="B29" s="23"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="23"/>
+      <x:c r="B30" s="23"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="23"/>
+      <x:c r="B31" s="23"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="23"/>
+      <x:c r="B32" s="23"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="23"/>
+      <x:c r="B33" s="23"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="23"/>
+      <x:c r="B34" s="23"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="23"/>
+      <x:c r="B35" s="23"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="23"/>
+      <x:c r="B36" s="23"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="23"/>
+      <x:c r="B37" s="23"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="23"/>
+      <x:c r="B38" s="23"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="23"/>
+      <x:c r="B39" s="23"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="23"/>
+      <x:c r="B40" s="23"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="23"/>
+      <x:c r="B41" s="23"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="23"/>
+      <x:c r="B42" s="23"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="23"/>
+      <x:c r="B43" s="23"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="23"/>
+      <x:c r="B44" s="23"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="23"/>
+      <x:c r="B45" s="23"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="23"/>
+      <x:c r="B46" s="23"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="23"/>
+      <x:c r="B47" s="23"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="23"/>
+      <x:c r="B48" s="23"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="23"/>
+      <x:c r="B49" s="23"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="23"/>
+      <x:c r="B50" s="23"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A1:B1"/>
+    <x:mergeCell ref="A2:B2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/downloads/editable-xlsx/LS-TMP-017_Test_Data_Table.xlsx
+++ b/downloads/editable-xlsx/LS-TMP-017_Test_Data_Table.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="1" r:id="Recbb5b9f46c948cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="2" r:id="Rbd5e297f84524de6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="1" r:id="R26b027ce90214077"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="2" r:id="Rce2c1d7fbea7407f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -387,7 +387,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="48" t="str">
-        <x:v>LS-TMP-017 Test Data Table Template</x:v>
+        <x:v>Test Data Table Template</x:v>
       </x:c>
       <x:c r="B1" s="48"/>
       <x:c r="C1" s="48"/>
